--- a/precios_oag_2026-05-26.xlsx
+++ b/precios_oag_2026-05-26.xlsx
@@ -554,7 +554,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Origen Agro Group | Precios McAllen TX vs CDMX | 26/05/2026 | TC: $17.27 MXN | Reporte USDA: 25/05/2026</t>
+          <t>Origen Agro Group | Precios McAllen TX vs CDMX | 26/05/2026 | TC: $17.29 MXN | Reporte USDA: 25/05/2026</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>$30.60</t>
+          <t>$30.63</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>$-15.40</t>
+          <t>$-15.37</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="M4" s="9" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>$36.03</t>
+          <t>$36.08</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -758,12 +758,12 @@
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>$+1.03</t>
+          <t>$+1.08</t>
         </is>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>+2.9%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="M5" s="13" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>$58.47</t>
+          <t>$58.54</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -826,12 +826,12 @@
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>$-1.53</t>
+          <t>$-1.46</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>$149.92</t>
+          <t>$150.09</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>$+84.92</t>
+          <t>$+85.09</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
-          <t>+130.6%</t>
+          <t>+130.9%</t>
         </is>
       </c>
       <c r="M7" s="13" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>$38.00</t>
+          <t>$38.04</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -962,12 +962,12 @@
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>$+8.00</t>
+          <t>$+8.04</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>+26.7%</t>
+          <t>+26.8%</t>
         </is>
       </c>
       <c r="M8" s="13" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>$22.44</t>
+          <t>$22.46</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>$+4.44</t>
+          <t>$+4.46</t>
         </is>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>+24.7%</t>
+          <t>+24.8%</t>
         </is>
       </c>
       <c r="M9" s="13" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>$18.42</t>
+          <t>$18.44</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>$-9.58</t>
+          <t>$-9.56</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-34.1%</t>
         </is>
       </c>
       <c r="M10" s="9" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>$25.70</t>
+          <t>$25.73</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>$-4.30</t>
+          <t>$-4.27</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-14.2%</t>
         </is>
       </c>
       <c r="M11" s="9" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>$22.84</t>
+          <t>$22.87</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>$+0.84</t>
+          <t>$+0.87</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>+3.8%</t>
+          <t>+4.0%</t>
         </is>
       </c>
       <c r="M12" s="13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>$14.66</t>
+          <t>$14.68</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1306,12 +1306,12 @@
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>$-10.34</t>
+          <t>$-10.32</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>-41.4%</t>
+          <t>-41.3%</t>
         </is>
       </c>
       <c r="M13" s="9" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>$18.09</t>
+          <t>$18.11</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>$+0.09</t>
+          <t>$+0.11</t>
         </is>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="M14" s="13" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>$22.84</t>
+          <t>$22.87</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>$+6.84</t>
+          <t>$+6.87</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>+42.8%</t>
+          <t>+42.9%</t>
         </is>
       </c>
       <c r="M15" s="13" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>$22.84</t>
+          <t>$22.87</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>$-2.16</t>
+          <t>$-2.13</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="M16" s="9" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>$10.31</t>
+          <t>$10.32</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>$22.84</t>
+          <t>$22.87</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>$+0.84</t>
+          <t>$+0.87</t>
         </is>
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
-          <t>+3.8%</t>
+          <t>+4.0%</t>
         </is>
       </c>
       <c r="M18" s="13" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>$20.17</t>
+          <t>$20.19</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>$22.84</t>
+          <t>$22.87</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>$+10.84</t>
+          <t>$+10.87</t>
         </is>
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
-          <t>+90.3%</t>
+          <t>+90.6%</t>
         </is>
       </c>
       <c r="M20" s="13" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>$13.87</t>
+          <t>$13.88</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>$-0.13</t>
+          <t>$-0.12</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>$13.33</t>
+          <t>$13.34</t>
         </is>
       </c>
       <c r="G22" s="15" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>$+1.33</t>
+          <t>$+1.34</t>
         </is>
       </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
-          <t>+11.1%</t>
+          <t>+11.2%</t>
         </is>
       </c>
       <c r="M22" s="13" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>$23.80</t>
+          <t>$23.82</t>
         </is>
       </c>
       <c r="G23" s="15" t="inlineStr">
@@ -2010,12 +2010,12 @@
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>$+8.80</t>
+          <t>$+8.82</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>+58.7%</t>
+          <t>+58.8%</t>
         </is>
       </c>
       <c r="M23" s="13" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>$13.33</t>
+          <t>$13.34</t>
         </is>
       </c>
       <c r="G24" s="15" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>$+1.33</t>
+          <t>$+1.34</t>
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr">
         <is>
-          <t>+11.1%</t>
+          <t>+11.2%</t>
         </is>
       </c>
       <c r="M24" s="13" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$20.01</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>$+5.99</t>
+          <t>$+6.01</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>+42.8%</t>
+          <t>+42.9%</t>
         </is>
       </c>
       <c r="M25" s="13" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>$22.84</t>
+          <t>$22.87</t>
         </is>
       </c>
       <c r="G26" s="15" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>$+10.84</t>
+          <t>$+10.87</t>
         </is>
       </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
-          <t>+90.3%</t>
+          <t>+90.6%</t>
         </is>
       </c>
       <c r="M26" s="13" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>$57.11</t>
+          <t>$57.18</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>$27.60</t>
+          <t>$27.63</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>$-0.40</t>
+          <t>$-0.37</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="M28" s="9" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>$41.88</t>
+          <t>$41.93</t>
         </is>
       </c>
       <c r="G29" s="15" t="inlineStr">
